--- a/Suppr-prescr/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
+++ b/Suppr-prescr/ig/StructureDefinition-fr-inpatient-pharmaceutical-intervention-suggestion.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T14:31:46+00:00</t>
+    <t>2026-05-25T08:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
